--- a/etf_holdings/2026-09-09_common_holdings_all.xlsx
+++ b/etf_holdings/2026-09-09_common_holdings_all.xlsx
@@ -649,7 +649,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>10.38%</t>
+          <t>10.25%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -662,7 +662,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>11.80%</t>
+          <t>11.76%</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -675,7 +675,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>9.14%</t>
+          <t>9.30%</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -688,7 +688,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>8.70%</t>
+          <t>8.62%</t>
         </is>
       </c>
       <c r="O2" t="n">
@@ -701,11 +701,11 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>15.86%</t>
+          <t>15.59%</t>
         </is>
       </c>
       <c r="R2" t="n">
-        <v>10100000</v>
+        <v>10000000</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -714,11 +714,11 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>13.65%</t>
+          <t>14.98%</t>
         </is>
       </c>
       <c r="U2" t="n">
-        <v>588000</v>
+        <v>637000</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>6.69%</t>
+          <t>6.61%</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -753,7 +753,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1.61%</t>
+          <t>1.60%</t>
         </is>
       </c>
       <c r="AD2" t="n">
@@ -779,7 +779,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>8.17%</t>
+          <t>8.33%</t>
         </is>
       </c>
       <c r="AJ2" t="n">
@@ -792,7 +792,7 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>8.91%</t>
+          <t>8.90%</t>
         </is>
       </c>
       <c r="AM2" t="n">
@@ -800,12 +800,12 @@
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>106.87%</t>
+          <t>107.90%</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>8.91%</t>
+          <t>8.99%</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
@@ -835,7 +835,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>8.65%</t>
+          <t>8.41%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -848,11 +848,11 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>5.33%</t>
+          <t>5.81%</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>900000</v>
+        <v>1000000</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -861,7 +861,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>5.85%</t>
+          <t>5.86%</t>
         </is>
       </c>
       <c r="L3" t="n">
@@ -874,7 +874,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>6.81%</t>
+          <t>6.64%</t>
         </is>
       </c>
       <c r="O3" t="n">
@@ -887,7 +887,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>6.62%</t>
+          <t>6.46%</t>
         </is>
       </c>
       <c r="R3" t="n">
@@ -900,7 +900,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>3.01%</t>
+          <t>3.00%</t>
         </is>
       </c>
       <c r="U3" t="n">
@@ -913,7 +913,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.66%</t>
+          <t>1.61%</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -939,7 +939,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>8.22%</t>
+          <t>8.06%</t>
         </is>
       </c>
       <c r="AD3" t="n">
@@ -965,7 +965,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>6.16%</t>
+          <t>6.18%</t>
         </is>
       </c>
       <c r="AJ3" t="n">
@@ -978,7 +978,7 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>7.72%</t>
+          <t>7.59%</t>
         </is>
       </c>
       <c r="AM3" t="n">
@@ -986,12 +986,12 @@
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>67.98%</t>
+          <t>67.57%</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>5.66%</t>
+          <t>5.63%</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>8.98%</t>
+          <t>8.95%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>9.27%</t>
+          <t>9.31%</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>3.69%</t>
+          <t>3.63%</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>5.43%</t>
+          <t>5.44%</t>
         </is>
       </c>
       <c r="R4" t="n">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2.70%</t>
+          <t>2.64%</t>
         </is>
       </c>
       <c r="U4" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>6.03%</t>
+          <t>6.00%</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>4.12%</t>
+          <t>4.14%</t>
         </is>
       </c>
       <c r="AD4" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>5.30%</t>
+          <t>5.21%</t>
         </is>
       </c>
       <c r="AJ4" t="n">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>3.26%</t>
+          <t>3.28%</t>
         </is>
       </c>
       <c r="AM4" t="n">
@@ -1172,12 +1172,12 @@
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>60.65%</t>
+          <t>60.47%</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>5.05%</t>
+          <t>5.04%</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>6.92%</t>
+          <t>7.05%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>5.16%</t>
+          <t>5.30%</t>
         </is>
       </c>
       <c r="I5" t="n">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2.26%</t>
+          <t>2.20%</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2.40%</t>
+          <t>2.45%</t>
         </is>
       </c>
       <c r="O5" t="n">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>5.95%</t>
+          <t>6.09%</t>
         </is>
       </c>
       <c r="R5" t="n">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1.68%</t>
+          <t>1.63%</t>
         </is>
       </c>
       <c r="U5" t="n">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>7.99%</t>
+          <t>8.13%</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>5.59%</t>
+          <t>5.74%</t>
         </is>
       </c>
       <c r="AD5" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>3.50%</t>
+          <t>3.40%</t>
         </is>
       </c>
       <c r="AJ5" t="n">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>4.32%</t>
+          <t>4.45%</t>
         </is>
       </c>
       <c r="AM5" t="n">
@@ -1358,12 +1358,12 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>52.90%</t>
+          <t>53.57%</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>4.41%</t>
+          <t>4.46%</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
@@ -1393,7 +1393,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>4.48%</t>
+          <t>4.57%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1406,11 +1406,11 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3.56%</t>
+          <t>3.42%</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1450000</v>
+        <v>1350000</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>1.80%</t>
+          <t>1.70%</t>
         </is>
       </c>
       <c r="L6" t="n">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2.38%</t>
+          <t>2.44%</t>
         </is>
       </c>
       <c r="O6" t="n">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2.87%</t>
+          <t>2.94%</t>
         </is>
       </c>
       <c r="R6" t="n">
@@ -1458,11 +1458,11 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1.92%</t>
+          <t>1.49%</t>
         </is>
       </c>
       <c r="U6" t="n">
-        <v>97000</v>
+        <v>80000</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>5.10%</t>
+          <t>5.20%</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>3.76%</t>
+          <t>3.87%</t>
         </is>
       </c>
       <c r="AD6" t="n">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>2.82%</t>
+          <t>2.66%</t>
         </is>
       </c>
       <c r="AJ6" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>1.55%</t>
+          <t>1.60%</t>
         </is>
       </c>
       <c r="AM6" t="n">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>33.94%</t>
+          <t>33.59%</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>2.83%</t>
+          <t>2.80%</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
